--- a/Demos [MTCars]/extended_mtcars.xlsx
+++ b/Demos [MTCars]/extended_mtcars.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agogo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agogo\Box\IS4487\Labs and Demos\is_4487_a9090\Demos [MTCars]\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5543DA65-FA62-4A94-8959-B0F3E2C64E0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2DD10DD-EBAB-42B0-9FEA-DF531CAFD7AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2967,25 +2967,22 @@
         <v>36</v>
       </c>
       <c r="B56">
-        <v>15.2</v>
+        <v>0</v>
       </c>
       <c r="C56">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D56">
-        <v>304</v>
+        <v>0</v>
       </c>
       <c r="E56">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F56">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="G56">
-        <v>3.4350000000000001</v>
-      </c>
-      <c r="H56">
-        <v>17.3</v>
+        <v>0</v>
       </c>
       <c r="I56">
         <v>0</v>
